--- a/docs/RabbitMQ queues.xlsx
+++ b/docs/RabbitMQ queues.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t xml:space="preserve">Queue/Channel Name</t>
   </si>
@@ -101,6 +101,15 @@
   </si>
   <si>
     <t xml:space="preserve">AI model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">workout.ai-reply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receives the full, generated workout plan from the AI Model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Model</t>
   </si>
 </sst>
 </file>
@@ -110,7 +119,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -146,6 +155,19 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -190,24 +212,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -407,7 +437,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.12"/>
   </cols>
   <sheetData>
@@ -525,7 +555,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="46.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
@@ -544,8 +574,26 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
     </row>
+    <row r="8" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="30.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D13" s="4"/>
+      <c r="D13" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/RabbitMQ queues.xlsx
+++ b/docs/RabbitMQ queues.xlsx
@@ -20,9 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
-  <si>
-    <t xml:space="preserve">Queue/Channel Name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+  <si>
+    <t xml:space="preserve">Queue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patterns</t>
   </si>
   <si>
     <t xml:space="preserve">Purpose</t>
@@ -37,9 +40,18 @@
     <t xml:space="preserve">Delivery Mechanism</t>
   </si>
   <si>
+    <t xml:space="preserve">Request Json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response Json</t>
+  </si>
+  <si>
     <t xml:space="preserve">chat-incoming</t>
   </si>
   <si>
+    <t xml:space="preserve">chat.incoming</t>
+  </si>
+  <si>
     <t xml:space="preserve">Receives a user's message payload.</t>
   </si>
   <si>
@@ -52,64 +64,105 @@
     <t xml:space="preserve">Asynchronous Task Processing</t>
   </si>
   <si>
-    <t xml:space="preserve">chat-outgoing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sends streaming response tokens back to the user.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real-time Streaming Push (via WebSocket)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notification-events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internal event to trigger the creation of a notification record in the database.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any Service (e.g., Chatbot, User Service)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notification Service (Worker)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notification-outgoing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sends a user-specific notification payload to be pushed in real-time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real-time WebSocket Push</t>
-  </si>
-  <si>
-    <t xml:space="preserve">broadcast.all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A special Routing Key used to send a single message intended for all active users.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real-time WebSocket Mass Push</t>
-  </si>
-  <si>
-    <t xml:space="preserve">workout.recommendation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sends a message to recommendation Ai model to recommend a workout plan based on user’s goal and data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">workout service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">workout.ai-reply</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receives the full, generated workout plan from the AI Model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Model</t>
+    <t xml:space="preserve">{
+ user_id: UUID;
+ message: string;
+ title: string | null;
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">history.getAll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">get all chat history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synchronous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+ user_id: string;
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+_id: string,
+user_id: UUID,
+title: string,
+createdAt: Date,
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">history.getById</t>
+  </si>
+  <si>
+    <t xml:space="preserve">get chat history by id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  _id: string,
+  user_id: UUID
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{  
+ _id: string;
+   user_id: string;
+   title: string;
+   Messages: {
+       role: "user" | “bot”,
+       content:string,
+       timestamp: Date
+     }[];
+   createdAt: Date;
+   updatedAt: Date;
+   __v: number | null; 
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">history.updateTitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for updating conversion title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  _id: string,
+  user_id: UUID,
+  title: string
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">history.delete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for deleting an exist converstion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{   _id: string,   user_id: UUID }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chatbot.queue.outgoingMessage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chat.outgoing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sends back to the user a chunk of Chat-bot response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asynchronous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+ user_id: string,
+ conversation_id: string,
+ chunk: string,
+ isFinal: boolean
+}</t>
   </si>
 </sst>
 </file>
@@ -150,9 +203,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Ubuntu"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -212,7 +265,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -225,12 +278,28 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -431,14 +500,16 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="38.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="38.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.41"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -457,143 +528,176 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+      <c r="B4" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="46.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="H7" s="6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="30.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D13" s="6"/>
+      <c r="E13" s="10"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/RabbitMQ queues.xlsx
+++ b/docs/RabbitMQ queues.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\graduation project\Fr3on fit\AI-trainer\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763DBD70-C180-47DF-9BE1-2D31DE6FD3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="now write in sheets all the wor" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="now write in sheets all the wor" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
@@ -22,73 +30,73 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
   <si>
-    <t xml:space="preserve">Queue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patterns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purpose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publisher (Source Service)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer (Worker Service)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delivery Mechanism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request Json</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Response Json</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chat-incoming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chat.incoming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receives a user's message payload.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API Gateway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chatbot Service (Worker)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asynchronous Task Processing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>Queue</t>
+  </si>
+  <si>
+    <t>Patterns</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Publisher (Source Service)</t>
+  </si>
+  <si>
+    <t>Consumer (Worker Service)</t>
+  </si>
+  <si>
+    <t>Delivery Mechanism</t>
+  </si>
+  <si>
+    <t>Request Json</t>
+  </si>
+  <si>
+    <t>Response Json</t>
+  </si>
+  <si>
+    <t>chat-incoming</t>
+  </si>
+  <si>
+    <t>chat.incoming</t>
+  </si>
+  <si>
+    <t>Receives a user's message payload.</t>
+  </si>
+  <si>
+    <t>API Gateway</t>
+  </si>
+  <si>
+    <t>Chatbot Service (Worker)</t>
+  </si>
+  <si>
+    <t>Asynchronous Task Processing</t>
+  </si>
+  <si>
+    <t>{
  user_id: UUID;
  message: string;
  title: string | null;
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">history.getAll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get all chat history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Synchronous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>NA</t>
+  </si>
+  <si>
+    <t>history.getAll</t>
+  </si>
+  <si>
+    <t>get all chat history</t>
+  </si>
+  <si>
+    <t>Synchronous</t>
+  </si>
+  <si>
+    <t>{
  user_id: string;
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">{
+    <t>{
 _id: string,
 user_id: UUID,
 title: string,
@@ -96,19 +104,19 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">history.getById</t>
-  </si>
-  <si>
-    <t xml:space="preserve">get chat history by id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>history.getById</t>
+  </si>
+  <si>
+    <t>get chat history by id</t>
+  </si>
+  <si>
+    <t>{
   _id: string,
   user_id: UUID
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">{  
+    <t>{  
  _id: string;
    user_id: string;
    title: string;
@@ -123,41 +131,41 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">history.updateTitle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">for updating conversion title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>history.updateTitle</t>
+  </si>
+  <si>
+    <t>for updating conversion title</t>
+  </si>
+  <si>
+    <t>{
   _id: string,
   user_id: UUID,
   title: string
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">history.delete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">for deleting an exist converstion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{   _id: string,   user_id: UUID }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chatbot.queue.outgoingMessage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chat.outgoing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sends back to the user a chunk of Chat-bot response</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asynchronous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
+    <t>history.delete</t>
+  </si>
+  <si>
+    <t>for deleting an exist converstion</t>
+  </si>
+  <si>
+    <t>{   _id: string,   user_id: UUID }</t>
+  </si>
+  <si>
+    <t>chatbot.queue.outgoingMessage</t>
+  </si>
+  <si>
+    <t>chat.outgoing</t>
+  </si>
+  <si>
+    <t>sends back to the user a chunk of Chat-bot response</t>
+  </si>
+  <si>
+    <t>Asynchronous</t>
+  </si>
+  <si>
+    <t>{
  user_id: string,
  conversation_id: string,
  chunk: string,
@@ -168,45 +176,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Ubuntu"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -218,9 +199,19 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Ubuntu"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -232,7 +223,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -240,139 +231,110 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285f4"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ea4335"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="fbbc04"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34a853"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="ff6d01"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46bdc6"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -402,7 +364,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -426,7 +388,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -486,226 +448,222 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="38.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="38.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.41"/>
+    <col min="1" max="1" width="24.21875" style="1" customWidth="1"/>
+    <col min="2" max="3" width="38.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="38.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.38671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" ht="13.8">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" ht="69">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="5" t="s">
+    <row r="3" spans="1:8" ht="82.8">
+      <c r="A3" s="5"/>
+      <c r="B3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="7" t="s">
+    <row r="4" spans="1:8" ht="179.4">
+      <c r="A4" s="5"/>
+      <c r="B4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="7" t="s">
+    <row r="5" spans="1:8" ht="179.4">
+      <c r="A5" s="5"/>
+      <c r="B5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:8" ht="179.4">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:8" ht="96.6">
+      <c r="A7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+    <row r="8" spans="1:8" ht="41.25" customHeight="1">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="30.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E13" s="10"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="10" spans="1:8" ht="30.15" customHeight="1"/>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+      <c r="E13" s="4"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/docs/RabbitMQ queues.xlsx
+++ b/docs/RabbitMQ queues.xlsx
@@ -1,25 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\graduation project\Fr3on fit\AI-trainer\docs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763DBD70-C180-47DF-9BE1-2D31DE6FD3AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="now write in sheets all the wor" sheetId="1" r:id="rId1"/>
+    <sheet name="now write in sheets all the wor" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
@@ -28,75 +20,80 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
-  <si>
-    <t>Queue</t>
-  </si>
-  <si>
-    <t>Patterns</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Publisher (Source Service)</t>
-  </si>
-  <si>
-    <t>Consumer (Worker Service)</t>
-  </si>
-  <si>
-    <t>Delivery Mechanism</t>
-  </si>
-  <si>
-    <t>Request Json</t>
-  </si>
-  <si>
-    <t>Response Json</t>
-  </si>
-  <si>
-    <t>chat-incoming</t>
-  </si>
-  <si>
-    <t>chat.incoming</t>
-  </si>
-  <si>
-    <t>Receives a user's message payload.</t>
-  </si>
-  <si>
-    <t>API Gateway</t>
-  </si>
-  <si>
-    <t>Chatbot Service (Worker)</t>
-  </si>
-  <si>
-    <t>Asynchronous Task Processing</t>
-  </si>
-  <si>
-    <t>{
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+  <si>
+    <t xml:space="preserve">Queue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patterns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purpose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publisher (Source Service)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer (Worker Service)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery Mechanism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request Json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response Json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chat-incoming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chat.incoming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receives a user's message payload.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API Gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatbot Service (Worker)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asynchronous Task Processing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
  user_id: UUID;
  message: string;
  title: string | null;
 }</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>history.getAll</t>
-  </si>
-  <si>
-    <t>get all chat history</t>
-  </si>
-  <si>
-    <t>Synchronous</t>
-  </si>
-  <si>
-    <t>{
+    <t xml:space="preserve">{
+ user_id: UUID,
+conversation_id: string,
+title: string,
+response: string
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">history.getAll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">get all chat history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Synchronous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
  user_id: string;
 }</t>
   </si>
   <si>
-    <t>{
+    <t xml:space="preserve">{
 _id: string,
 user_id: UUID,
 title: string,
@@ -104,19 +101,19 @@
 }</t>
   </si>
   <si>
-    <t>history.getById</t>
-  </si>
-  <si>
-    <t>get chat history by id</t>
-  </si>
-  <si>
-    <t>{
+    <t xml:space="preserve">history.getById</t>
+  </si>
+  <si>
+    <t xml:space="preserve">get chat history by id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
   _id: string,
   user_id: UUID
 }</t>
   </si>
   <si>
-    <t>{  
+    <t xml:space="preserve">{  
  _id: string;
    user_id: string;
    title: string;
@@ -131,63 +128,68 @@
 }</t>
   </si>
   <si>
-    <t>history.updateTitle</t>
-  </si>
-  <si>
-    <t>for updating conversion title</t>
-  </si>
-  <si>
-    <t>{
+    <t xml:space="preserve">history.updateTitle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for updating conversion title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
   _id: string,
   user_id: UUID,
   title: string
 }</t>
   </si>
   <si>
-    <t>history.delete</t>
-  </si>
-  <si>
-    <t>for deleting an exist converstion</t>
-  </si>
-  <si>
-    <t>{   _id: string,   user_id: UUID }</t>
-  </si>
-  <si>
-    <t>chatbot.queue.outgoingMessage</t>
-  </si>
-  <si>
-    <t>chat.outgoing</t>
-  </si>
-  <si>
-    <t>sends back to the user a chunk of Chat-bot response</t>
-  </si>
-  <si>
-    <t>Asynchronous</t>
-  </si>
-  <si>
-    <t>{
- user_id: string,
- conversation_id: string,
- chunk: string,
- isFinal: boolean
-}</t>
+    <t xml:space="preserve">history.delete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for deleting an exist converstion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{   _id: string,   user_id: UUID }</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Ubuntu"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -199,31 +201,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Ubuntu"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3465A4"/>
+        <bgColor rgb="FF3366FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -231,110 +230,203 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF3465A4"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4285f4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ea4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="fbbc04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="34a853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="ff6d01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="46bdc6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="1155cc"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -364,7 +456,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -388,7 +480,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -448,222 +540,210 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="12.609375" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.61328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="24.21875" style="1" customWidth="1"/>
-    <col min="2" max="3" width="38.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="38.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.38671875" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="38.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="38.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30.77"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13.8">
-      <c r="A1" s="5" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="69">
-      <c r="A2" s="5" t="s">
+    <row r="2" customFormat="false" ht="75.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="82.8">
-      <c r="A3" s="5"/>
-      <c r="B3" s="8" t="s">
+    <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="179.4">
-      <c r="A4" s="5"/>
-      <c r="B4" s="10" t="s">
+    <row r="4" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="179.4">
-      <c r="A5" s="5"/>
-      <c r="B5" s="10" t="s">
+    <row r="5" customFormat="false" ht="166.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="179.4">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5" t="s">
+    <row r="6" customFormat="false" ht="161.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="96.6">
-      <c r="A7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="41.25" customHeight="1">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="10" spans="1:8" ht="30.15" customHeight="1"/>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
-      <c r="E13" s="4"/>
+    <row r="7" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="9"/>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E13" s="11"/>
     </row>
   </sheetData>
-  <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>